--- a/star_wars_order.xlsx
+++ b/star_wars_order.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Star Wars Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Chronological Order" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Release Order" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -112,9 +113,6 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -122,6 +120,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -489,14 +490,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="4" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
-    <col width="28" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -505,199 +503,241 @@
           <t>Chronological Order</t>
         </is>
       </c>
-      <c r="D1" s="2" t="inlineStr">
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Movie Title</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>The Phantom Menace</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>Attack of the Clones</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Revenge of the Sith</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>A New Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>The Empire Strikes Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>Return of the Jedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>The Force Awakens</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>The Last Jedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="24" customHeight="1">
+      <c r="A11" s="3" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>The Rise of Skywalker</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:B1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
         <is>
           <t>Release Order</t>
         </is>
       </c>
     </row>
     <row r="2" ht="24" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>Movie Title</t>
         </is>
       </c>
-      <c r="D2" s="3" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
-        <is>
-          <t>Movie Title</t>
-        </is>
-      </c>
     </row>
     <row r="3" ht="24" customHeight="1">
-      <c r="A3" s="4" t="n">
+      <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="4" t="inlineStr">
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>A New Hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>The Empire Strikes Back</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>Return of the Jedi</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
         <is>
           <t>The Phantom Menace</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>A New Hope</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="24" customHeight="1">
-      <c r="A4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="B4" s="5" t="inlineStr">
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="3" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Attack of the Clones</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="E4" s="5" t="inlineStr">
-        <is>
-          <t>The Empire Strikes Back</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="24" customHeight="1">
-      <c r="A5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="inlineStr">
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
         <is>
           <t>Revenge of the Sith</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="E5" s="4" t="inlineStr">
-        <is>
-          <t>Return of the Jedi</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="24" customHeight="1">
-      <c r="A6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>A New Hope</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E6" s="5" t="inlineStr">
-        <is>
-          <t>The Phantom Menace</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="24" customHeight="1">
-      <c r="A7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="B7" s="4" t="inlineStr">
-        <is>
-          <t>The Empire Strikes Back</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>Attack of the Clones</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="24" customHeight="1">
-      <c r="A8" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Return of the Jedi</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="E8" s="5" t="inlineStr">
-        <is>
-          <t>Revenge of the Sith</t>
-        </is>
-      </c>
     </row>
     <row r="9" ht="24" customHeight="1">
-      <c r="A9" s="4" t="n">
+      <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="4" t="inlineStr">
+      <c r="B9" s="3" t="inlineStr">
         <is>
           <t>The Force Awakens</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>The Force Awakens</t>
-        </is>
-      </c>
     </row>
     <row r="10" ht="24" customHeight="1">
-      <c r="A10" s="5" t="n">
+      <c r="A10" s="4" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="4" t="inlineStr">
         <is>
           <t>The Last Jedi</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
-        <v>8</v>
-      </c>
-      <c r="E10" s="5" t="inlineStr">
-        <is>
-          <t>The Last Jedi</t>
-        </is>
-      </c>
     </row>
     <row r="11" ht="24" customHeight="1">
-      <c r="A11" s="4" t="n">
+      <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="4" t="inlineStr">
+      <c r="B11" s="3" t="inlineStr">
         <is>
           <t>The Rise of Skywalker</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>The Rise of Skywalker</t>
-        </is>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="D1:E1"/>
+  <mergeCells count="1">
     <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/star_wars_order.xlsx
+++ b/star_wars_order.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="Chronological Order" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Release Order" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Characters" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -82,7 +83,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -104,11 +105,44 @@
         <color rgb="00FFD700"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FFD700"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00FFD700"/>
+      </right>
+      <top style="thin">
+        <color rgb="00FFD700"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00FFD700"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -125,6 +159,7 @@
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -503,6 +538,7 @@
           <t>Chronological Order</t>
         </is>
       </c>
+      <c r="B1" s="6" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -633,6 +669,7 @@
           <t>Release Order</t>
         </is>
       </c>
+      <c r="B1" s="6" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -742,4 +779,9536 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B901"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="28" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Luke Skywalker</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="24" customHeight="1">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="inlineStr">
+        <is>
+          <t>Luke Skywalker</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="24" customHeight="1">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="24" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>blond</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="24" customHeight="1">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="24" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>19BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="24" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="24" customHeight="1">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>C-3PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="24" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>C-3PO</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="24" customHeight="1">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="24" customHeight="1">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="24" customHeight="1">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="24" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="24" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>112BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="24" customHeight="1">
+      <c r="A21" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="24" customHeight="1">
+      <c r="A23" s="1" t="inlineStr">
+        <is>
+          <t>R2-D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="24" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="24" customHeight="1">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="inlineStr">
+        <is>
+          <t>R2-D2</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="24" customHeight="1">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B26" s="4" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="24" customHeight="1">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="24" customHeight="1">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="inlineStr">
+        <is>
+          <t>white, blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="24" customHeight="1">
+      <c r="A30" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B30" s="4" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="24" customHeight="1">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>33BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="24" customHeight="1">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>Darth Vader</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="24" customHeight="1">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="24" customHeight="1">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>Darth Vader</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B37" s="4" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="24" customHeight="1">
+      <c r="A39" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="24" customHeight="1">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="24" customHeight="1">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>41.9BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="24" customHeight="1">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1">
+      <c r="A45" s="1" t="inlineStr">
+        <is>
+          <t>Leia Organa</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="24" customHeight="1">
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="inlineStr">
+        <is>
+          <t>Leia Organa</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="24" customHeight="1">
+      <c r="A48" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B48" s="4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="24" customHeight="1">
+      <c r="A49" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="inlineStr">
+        <is>
+          <t>49</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="24" customHeight="1">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="24" customHeight="1">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="24" customHeight="1">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="24" customHeight="1">
+      <c r="A53" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="inlineStr">
+        <is>
+          <t>19BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="24" customHeight="1">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="24" customHeight="1">
+      <c r="A56" s="1" t="inlineStr">
+        <is>
+          <t>Owen Lars</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="24" customHeight="1">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="A58" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="inlineStr">
+        <is>
+          <t>Owen Lars</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="24" customHeight="1">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B59" s="4" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="24" customHeight="1">
+      <c r="A60" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="24" customHeight="1">
+      <c r="A61" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B61" s="4" t="inlineStr">
+        <is>
+          <t>brown, grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="24" customHeight="1">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="24" customHeight="1">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B63" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="24" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="inlineStr">
+        <is>
+          <t>52BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="24" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="24" customHeight="1">
+      <c r="A67" s="1" t="inlineStr">
+        <is>
+          <t>Beru Whitesun lars</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="24" customHeight="1">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="24" customHeight="1">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Beru Whitesun lars</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="24" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="24" customHeight="1">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B71" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="24" customHeight="1">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="24" customHeight="1">
+      <c r="A73" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B73" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="24" customHeight="1">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="24" customHeight="1">
+      <c r="A75" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B75" s="3" t="inlineStr">
+        <is>
+          <t>47BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="24" customHeight="1">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="24" customHeight="1">
+      <c r="A78" s="1" t="inlineStr">
+        <is>
+          <t>R5-D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="24" customHeight="1">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="24" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B80" s="3" t="inlineStr">
+        <is>
+          <t>R5-D4</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="24" customHeight="1">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B81" s="4" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="24" customHeight="1">
+      <c r="A82" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B82" s="3" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="24" customHeight="1">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B83" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="24" customHeight="1">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B84" s="3" t="inlineStr">
+        <is>
+          <t>white, red</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="24" customHeight="1">
+      <c r="A85" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B85" s="4" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="24" customHeight="1">
+      <c r="A86" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B86" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="24" customHeight="1">
+      <c r="A87" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B87" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="24" customHeight="1">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>Biggs Darklighter</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="24" customHeight="1">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="24" customHeight="1">
+      <c r="A91" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Biggs Darklighter</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="24" customHeight="1">
+      <c r="A92" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B92" s="4" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="24" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="24" customHeight="1">
+      <c r="A94" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B94" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="24" customHeight="1">
+      <c r="A95" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B95" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="24" customHeight="1">
+      <c r="A96" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B96" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="24" customHeight="1">
+      <c r="A97" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B97" s="3" t="inlineStr">
+        <is>
+          <t>24BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="24" customHeight="1">
+      <c r="A98" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B98" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="24" customHeight="1">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>Obi-Wan Kenobi</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="24" customHeight="1">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="24" customHeight="1">
+      <c r="A102" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B102" s="3" t="inlineStr">
+        <is>
+          <t>Obi-Wan Kenobi</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="24" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B103" s="4" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="24" customHeight="1">
+      <c r="A104" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="24" customHeight="1">
+      <c r="A105" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B105" s="4" t="inlineStr">
+        <is>
+          <t>auburn, white</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="24" customHeight="1">
+      <c r="A106" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B106" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="24" customHeight="1">
+      <c r="A107" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B107" s="4" t="inlineStr">
+        <is>
+          <t>blue-gray</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="24" customHeight="1">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B108" s="3" t="inlineStr">
+        <is>
+          <t>57BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="24" customHeight="1">
+      <c r="A109" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B109" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="111" ht="24" customHeight="1">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>Anakin Skywalker</t>
+        </is>
+      </c>
+    </row>
+    <row r="112" ht="24" customHeight="1">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="24" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B113" s="3" t="inlineStr">
+        <is>
+          <t>Anakin Skywalker</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="24" customHeight="1">
+      <c r="A114" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B114" s="4" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="115" ht="24" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B115" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="24" customHeight="1">
+      <c r="A116" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B116" s="4" t="inlineStr">
+        <is>
+          <t>blond</t>
+        </is>
+      </c>
+    </row>
+    <row r="117" ht="24" customHeight="1">
+      <c r="A117" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B117" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="118" ht="24" customHeight="1">
+      <c r="A118" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B118" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="24" customHeight="1">
+      <c r="A119" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B119" s="3" t="inlineStr">
+        <is>
+          <t>41.9BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="24" customHeight="1">
+      <c r="A120" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B120" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="122" ht="24" customHeight="1">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>Wilhuff Tarkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="123" ht="24" customHeight="1">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="24" customHeight="1">
+      <c r="A124" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B124" s="3" t="inlineStr">
+        <is>
+          <t>Wilhuff Tarkin</t>
+        </is>
+      </c>
+    </row>
+    <row r="125" ht="24" customHeight="1">
+      <c r="A125" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B125" s="4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="126" ht="24" customHeight="1">
+      <c r="A126" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B126" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="127" ht="24" customHeight="1">
+      <c r="A127" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B127" s="4" t="inlineStr">
+        <is>
+          <t>auburn, grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="128" ht="24" customHeight="1">
+      <c r="A128" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B128" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="24" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B129" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="130" ht="24" customHeight="1">
+      <c r="A130" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B130" s="3" t="inlineStr">
+        <is>
+          <t>64BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="131" ht="24" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B131" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="133" ht="24" customHeight="1">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>Chewbacca</t>
+        </is>
+      </c>
+    </row>
+    <row r="134" ht="24" customHeight="1">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="135" ht="24" customHeight="1">
+      <c r="A135" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B135" s="3" t="inlineStr">
+        <is>
+          <t>Chewbacca</t>
+        </is>
+      </c>
+    </row>
+    <row r="136" ht="24" customHeight="1">
+      <c r="A136" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B136" s="4" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+    </row>
+    <row r="137" ht="24" customHeight="1">
+      <c r="A137" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B137" s="3" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+    </row>
+    <row r="138" ht="24" customHeight="1">
+      <c r="A138" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B138" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="139" ht="24" customHeight="1">
+      <c r="A139" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B139" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="140" ht="24" customHeight="1">
+      <c r="A140" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B140" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="141" ht="24" customHeight="1">
+      <c r="A141" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B141" s="3" t="inlineStr">
+        <is>
+          <t>200BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="142" ht="24" customHeight="1">
+      <c r="A142" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B142" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="24" customHeight="1">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>Han Solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="24" customHeight="1">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="24" customHeight="1">
+      <c r="A146" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B146" s="3" t="inlineStr">
+        <is>
+          <t>Han Solo</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="24" customHeight="1">
+      <c r="A147" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B147" s="4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="148" ht="24" customHeight="1">
+      <c r="A148" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B148" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="149" ht="24" customHeight="1">
+      <c r="A149" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B149" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="150" ht="24" customHeight="1">
+      <c r="A150" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B150" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="151" ht="24" customHeight="1">
+      <c r="A151" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B151" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="152" ht="24" customHeight="1">
+      <c r="A152" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B152" s="3" t="inlineStr">
+        <is>
+          <t>29BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="153" ht="24" customHeight="1">
+      <c r="A153" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B153" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" ht="24" customHeight="1">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>Greedo</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" ht="24" customHeight="1">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" ht="24" customHeight="1">
+      <c r="A157" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B157" s="3" t="inlineStr">
+        <is>
+          <t>Greedo</t>
+        </is>
+      </c>
+    </row>
+    <row r="158" ht="24" customHeight="1">
+      <c r="A158" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B158" s="4" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="159" ht="24" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B159" s="3" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+    </row>
+    <row r="160" ht="24" customHeight="1">
+      <c r="A160" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B160" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="161" ht="24" customHeight="1">
+      <c r="A161" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B161" s="3" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="162" ht="24" customHeight="1">
+      <c r="A162" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B162" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="163" ht="24" customHeight="1">
+      <c r="A163" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B163" s="3" t="inlineStr">
+        <is>
+          <t>44BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="164" ht="24" customHeight="1">
+      <c r="A164" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B164" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="166" ht="24" customHeight="1">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>Jabba Desilijic Tiure</t>
+        </is>
+      </c>
+    </row>
+    <row r="167" ht="24" customHeight="1">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="168" ht="24" customHeight="1">
+      <c r="A168" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B168" s="3" t="inlineStr">
+        <is>
+          <t>Jabba Desilijic Tiure</t>
+        </is>
+      </c>
+    </row>
+    <row r="169" ht="24" customHeight="1">
+      <c r="A169" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B169" s="4" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="170" ht="24" customHeight="1">
+      <c r="A170" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B170" s="3" t="inlineStr">
+        <is>
+          <t>1,358</t>
+        </is>
+      </c>
+    </row>
+    <row r="171" ht="24" customHeight="1">
+      <c r="A171" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B171" s="4" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+    </row>
+    <row r="172" ht="24" customHeight="1">
+      <c r="A172" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B172" s="3" t="inlineStr">
+        <is>
+          <t>green-tan, brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="173" ht="24" customHeight="1">
+      <c r="A173" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B173" s="4" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="174" ht="24" customHeight="1">
+      <c r="A174" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B174" s="3" t="inlineStr">
+        <is>
+          <t>600BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="175" ht="24" customHeight="1">
+      <c r="A175" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B175" s="4" t="inlineStr">
+        <is>
+          <t>hermaphrodite</t>
+        </is>
+      </c>
+    </row>
+    <row r="177" ht="24" customHeight="1">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>Wedge Antilles</t>
+        </is>
+      </c>
+    </row>
+    <row r="178" ht="24" customHeight="1">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="179" ht="24" customHeight="1">
+      <c r="A179" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B179" s="3" t="inlineStr">
+        <is>
+          <t>Wedge Antilles</t>
+        </is>
+      </c>
+    </row>
+    <row r="180" ht="24" customHeight="1">
+      <c r="A180" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B180" s="4" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="181" ht="24" customHeight="1">
+      <c r="A181" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B181" s="3" t="inlineStr">
+        <is>
+          <t>77</t>
+        </is>
+      </c>
+    </row>
+    <row r="182" ht="24" customHeight="1">
+      <c r="A182" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B182" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="183" ht="24" customHeight="1">
+      <c r="A183" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B183" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="184" ht="24" customHeight="1">
+      <c r="A184" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B184" s="4" t="inlineStr">
+        <is>
+          <t>hazel</t>
+        </is>
+      </c>
+    </row>
+    <row r="185" ht="24" customHeight="1">
+      <c r="A185" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B185" s="3" t="inlineStr">
+        <is>
+          <t>21BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="186" ht="24" customHeight="1">
+      <c r="A186" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B186" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="188" ht="24" customHeight="1">
+      <c r="A188" s="1" t="inlineStr">
+        <is>
+          <t>Jek Tono Porkins</t>
+        </is>
+      </c>
+    </row>
+    <row r="189" ht="24" customHeight="1">
+      <c r="A189" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="190" ht="24" customHeight="1">
+      <c r="A190" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B190" s="3" t="inlineStr">
+        <is>
+          <t>Jek Tono Porkins</t>
+        </is>
+      </c>
+    </row>
+    <row r="191" ht="24" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B191" s="4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="192" ht="24" customHeight="1">
+      <c r="A192" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B192" s="3" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+    </row>
+    <row r="193" ht="24" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B193" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="194" ht="24" customHeight="1">
+      <c r="A194" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B194" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="195" ht="24" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B195" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="196" ht="24" customHeight="1">
+      <c r="A196" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B196" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="197" ht="24" customHeight="1">
+      <c r="A197" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B197" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="199" ht="24" customHeight="1">
+      <c r="A199" s="1" t="inlineStr">
+        <is>
+          <t>Yoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="200" ht="24" customHeight="1">
+      <c r="A200" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B200" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="201" ht="24" customHeight="1">
+      <c r="A201" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B201" s="3" t="inlineStr">
+        <is>
+          <t>Yoda</t>
+        </is>
+      </c>
+    </row>
+    <row r="202" ht="24" customHeight="1">
+      <c r="A202" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B202" s="4" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="203" ht="24" customHeight="1">
+      <c r="A203" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B203" s="3" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+    </row>
+    <row r="204" ht="24" customHeight="1">
+      <c r="A204" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B204" s="4" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+    </row>
+    <row r="205" ht="24" customHeight="1">
+      <c r="A205" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B205" s="3" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="206" ht="24" customHeight="1">
+      <c r="A206" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B206" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="207" ht="24" customHeight="1">
+      <c r="A207" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B207" s="3" t="inlineStr">
+        <is>
+          <t>896BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="208" ht="24" customHeight="1">
+      <c r="A208" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B208" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="210" ht="24" customHeight="1">
+      <c r="A210" s="1" t="inlineStr">
+        <is>
+          <t>Palpatine</t>
+        </is>
+      </c>
+    </row>
+    <row r="211" ht="24" customHeight="1">
+      <c r="A211" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B211" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="212" ht="24" customHeight="1">
+      <c r="A212" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B212" s="3" t="inlineStr">
+        <is>
+          <t>Palpatine</t>
+        </is>
+      </c>
+    </row>
+    <row r="213" ht="24" customHeight="1">
+      <c r="A213" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B213" s="4" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="214" ht="24" customHeight="1">
+      <c r="A214" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B214" s="3" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+    </row>
+    <row r="215" ht="24" customHeight="1">
+      <c r="A215" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B215" s="4" t="inlineStr">
+        <is>
+          <t>grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="216" ht="24" customHeight="1">
+      <c r="A216" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B216" s="3" t="inlineStr">
+        <is>
+          <t>pale</t>
+        </is>
+      </c>
+    </row>
+    <row r="217" ht="24" customHeight="1">
+      <c r="A217" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B217" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="218" ht="24" customHeight="1">
+      <c r="A218" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B218" s="3" t="inlineStr">
+        <is>
+          <t>82BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="219" ht="24" customHeight="1">
+      <c r="A219" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B219" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="221" ht="24" customHeight="1">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>Boba Fett</t>
+        </is>
+      </c>
+    </row>
+    <row r="222" ht="24" customHeight="1">
+      <c r="A222" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="223" ht="24" customHeight="1">
+      <c r="A223" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B223" s="3" t="inlineStr">
+        <is>
+          <t>Boba Fett</t>
+        </is>
+      </c>
+    </row>
+    <row r="224" ht="24" customHeight="1">
+      <c r="A224" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B224" s="4" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="225" ht="24" customHeight="1">
+      <c r="A225" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B225" s="3" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="226" ht="24" customHeight="1">
+      <c r="A226" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B226" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="227" ht="24" customHeight="1">
+      <c r="A227" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B227" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="228" ht="24" customHeight="1">
+      <c r="A228" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B228" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="229" ht="24" customHeight="1">
+      <c r="A229" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B229" s="3" t="inlineStr">
+        <is>
+          <t>31.5BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="230" ht="24" customHeight="1">
+      <c r="A230" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B230" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="232" ht="24" customHeight="1">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>IG-88</t>
+        </is>
+      </c>
+    </row>
+    <row r="233" ht="24" customHeight="1">
+      <c r="A233" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B233" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="234" ht="24" customHeight="1">
+      <c r="A234" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B234" s="3" t="inlineStr">
+        <is>
+          <t>IG-88</t>
+        </is>
+      </c>
+    </row>
+    <row r="235" ht="24" customHeight="1">
+      <c r="A235" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B235" s="4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+    </row>
+    <row r="236" ht="24" customHeight="1">
+      <c r="A236" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B236" s="3" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+    </row>
+    <row r="237" ht="24" customHeight="1">
+      <c r="A237" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B237" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="238" ht="24" customHeight="1">
+      <c r="A238" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B238" s="3" t="inlineStr">
+        <is>
+          <t>metal</t>
+        </is>
+      </c>
+    </row>
+    <row r="239" ht="24" customHeight="1">
+      <c r="A239" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B239" s="4" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="240" ht="24" customHeight="1">
+      <c r="A240" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B240" s="3" t="inlineStr">
+        <is>
+          <t>15BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="241" ht="24" customHeight="1">
+      <c r="A241" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B241" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="243" ht="24" customHeight="1">
+      <c r="A243" s="1" t="inlineStr">
+        <is>
+          <t>Bossk</t>
+        </is>
+      </c>
+    </row>
+    <row r="244" ht="24" customHeight="1">
+      <c r="A244" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B244" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="245" ht="24" customHeight="1">
+      <c r="A245" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B245" s="3" t="inlineStr">
+        <is>
+          <t>Bossk</t>
+        </is>
+      </c>
+    </row>
+    <row r="246" ht="24" customHeight="1">
+      <c r="A246" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B246" s="4" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+    </row>
+    <row r="247" ht="24" customHeight="1">
+      <c r="A247" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B247" s="3" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+    </row>
+    <row r="248" ht="24" customHeight="1">
+      <c r="A248" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B248" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="249" ht="24" customHeight="1">
+      <c r="A249" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B249" s="3" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="250" ht="24" customHeight="1">
+      <c r="A250" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B250" s="4" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="251" ht="24" customHeight="1">
+      <c r="A251" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B251" s="3" t="inlineStr">
+        <is>
+          <t>53BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="252" ht="24" customHeight="1">
+      <c r="A252" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B252" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="254" ht="24" customHeight="1">
+      <c r="A254" s="1" t="inlineStr">
+        <is>
+          <t>Lando Calrissian</t>
+        </is>
+      </c>
+    </row>
+    <row r="255" ht="24" customHeight="1">
+      <c r="A255" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B255" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="256" ht="24" customHeight="1">
+      <c r="A256" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B256" s="3" t="inlineStr">
+        <is>
+          <t>Lando Calrissian</t>
+        </is>
+      </c>
+    </row>
+    <row r="257" ht="24" customHeight="1">
+      <c r="A257" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B257" s="4" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+    </row>
+    <row r="258" ht="24" customHeight="1">
+      <c r="A258" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B258" s="3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="259" ht="24" customHeight="1">
+      <c r="A259" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B259" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="24" customHeight="1">
+      <c r="A260" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B260" s="3" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="261" ht="24" customHeight="1">
+      <c r="A261" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B261" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="262" ht="24" customHeight="1">
+      <c r="A262" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B262" s="3" t="inlineStr">
+        <is>
+          <t>31BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="24" customHeight="1">
+      <c r="A263" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B263" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="265" ht="24" customHeight="1">
+      <c r="A265" s="1" t="inlineStr">
+        <is>
+          <t>Lobot</t>
+        </is>
+      </c>
+    </row>
+    <row r="266" ht="24" customHeight="1">
+      <c r="A266" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="24" customHeight="1">
+      <c r="A267" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B267" s="3" t="inlineStr">
+        <is>
+          <t>Lobot</t>
+        </is>
+      </c>
+    </row>
+    <row r="268" ht="24" customHeight="1">
+      <c r="A268" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B268" s="4" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="269" ht="24" customHeight="1">
+      <c r="A269" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B269" s="3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="270" ht="24" customHeight="1">
+      <c r="A270" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B270" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="271" ht="24" customHeight="1">
+      <c r="A271" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B271" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="272" ht="24" customHeight="1">
+      <c r="A272" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B272" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="273" ht="24" customHeight="1">
+      <c r="A273" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B273" s="3" t="inlineStr">
+        <is>
+          <t>37BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="274" ht="24" customHeight="1">
+      <c r="A274" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B274" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="276" ht="24" customHeight="1">
+      <c r="A276" s="1" t="inlineStr">
+        <is>
+          <t>Ackbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="277" ht="24" customHeight="1">
+      <c r="A277" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B277" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="278" ht="24" customHeight="1">
+      <c r="A278" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B278" s="3" t="inlineStr">
+        <is>
+          <t>Ackbar</t>
+        </is>
+      </c>
+    </row>
+    <row r="279" ht="24" customHeight="1">
+      <c r="A279" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B279" s="4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="280" ht="24" customHeight="1">
+      <c r="A280" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B280" s="3" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+    </row>
+    <row r="281" ht="24" customHeight="1">
+      <c r="A281" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B281" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="282" ht="24" customHeight="1">
+      <c r="A282" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B282" s="3" t="inlineStr">
+        <is>
+          <t>brown mottle</t>
+        </is>
+      </c>
+    </row>
+    <row r="283" ht="24" customHeight="1">
+      <c r="A283" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B283" s="4" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="284" ht="24" customHeight="1">
+      <c r="A284" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B284" s="3" t="inlineStr">
+        <is>
+          <t>41BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="285" ht="24" customHeight="1">
+      <c r="A285" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B285" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="287" ht="24" customHeight="1">
+      <c r="A287" s="1" t="inlineStr">
+        <is>
+          <t>Mon Mothma</t>
+        </is>
+      </c>
+    </row>
+    <row r="288" ht="24" customHeight="1">
+      <c r="A288" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B288" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="289" ht="24" customHeight="1">
+      <c r="A289" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B289" s="3" t="inlineStr">
+        <is>
+          <t>Mon Mothma</t>
+        </is>
+      </c>
+    </row>
+    <row r="290" ht="24" customHeight="1">
+      <c r="A290" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B290" s="4" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+    </row>
+    <row r="291" ht="24" customHeight="1">
+      <c r="A291" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B291" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="292" ht="24" customHeight="1">
+      <c r="A292" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B292" s="4" t="inlineStr">
+        <is>
+          <t>auburn</t>
+        </is>
+      </c>
+    </row>
+    <row r="293" ht="24" customHeight="1">
+      <c r="A293" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B293" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="24" customHeight="1">
+      <c r="A294" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B294" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="295" ht="24" customHeight="1">
+      <c r="A295" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B295" s="3" t="inlineStr">
+        <is>
+          <t>48BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="296" ht="24" customHeight="1">
+      <c r="A296" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B296" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="298" ht="24" customHeight="1">
+      <c r="A298" s="1" t="inlineStr">
+        <is>
+          <t>Arvel Crynyd</t>
+        </is>
+      </c>
+    </row>
+    <row r="299" ht="24" customHeight="1">
+      <c r="A299" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B299" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="300" ht="24" customHeight="1">
+      <c r="A300" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B300" s="3" t="inlineStr">
+        <is>
+          <t>Arvel Crynyd</t>
+        </is>
+      </c>
+    </row>
+    <row r="301" ht="24" customHeight="1">
+      <c r="A301" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B301" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="302" ht="24" customHeight="1">
+      <c r="A302" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B302" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="303" ht="24" customHeight="1">
+      <c r="A303" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B303" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="304" ht="24" customHeight="1">
+      <c r="A304" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B304" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="305" ht="24" customHeight="1">
+      <c r="A305" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B305" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="306" ht="24" customHeight="1">
+      <c r="A306" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B306" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="307" ht="24" customHeight="1">
+      <c r="A307" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B307" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="309" ht="24" customHeight="1">
+      <c r="A309" s="1" t="inlineStr">
+        <is>
+          <t>Wicket Systri Warrick</t>
+        </is>
+      </c>
+    </row>
+    <row r="310" ht="24" customHeight="1">
+      <c r="A310" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B310" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="311" ht="24" customHeight="1">
+      <c r="A311" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B311" s="3" t="inlineStr">
+        <is>
+          <t>Wicket Systri Warrick</t>
+        </is>
+      </c>
+    </row>
+    <row r="312" ht="24" customHeight="1">
+      <c r="A312" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B312" s="4" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="313" ht="24" customHeight="1">
+      <c r="A313" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B313" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="314" ht="24" customHeight="1">
+      <c r="A314" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B314" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="315" ht="24" customHeight="1">
+      <c r="A315" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B315" s="3" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="316" ht="24" customHeight="1">
+      <c r="A316" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B316" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="317" ht="24" customHeight="1">
+      <c r="A317" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B317" s="3" t="inlineStr">
+        <is>
+          <t>8BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="318" ht="24" customHeight="1">
+      <c r="A318" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B318" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="320" ht="24" customHeight="1">
+      <c r="A320" s="1" t="inlineStr">
+        <is>
+          <t>Nien Nunb</t>
+        </is>
+      </c>
+    </row>
+    <row r="321" ht="24" customHeight="1">
+      <c r="A321" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B321" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="322" ht="24" customHeight="1">
+      <c r="A322" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B322" s="3" t="inlineStr">
+        <is>
+          <t>Nien Nunb</t>
+        </is>
+      </c>
+    </row>
+    <row r="323" ht="24" customHeight="1">
+      <c r="A323" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B323" s="4" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+    </row>
+    <row r="324" ht="24" customHeight="1">
+      <c r="A324" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B324" s="3" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+    </row>
+    <row r="325" ht="24" customHeight="1">
+      <c r="A325" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B325" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="326" ht="24" customHeight="1">
+      <c r="A326" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B326" s="3" t="inlineStr">
+        <is>
+          <t>grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="327" ht="24" customHeight="1">
+      <c r="A327" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B327" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="328" ht="24" customHeight="1">
+      <c r="A328" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B328" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="329" ht="24" customHeight="1">
+      <c r="A329" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B329" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="331" ht="24" customHeight="1">
+      <c r="A331" s="1" t="inlineStr">
+        <is>
+          <t>Qui-Gon Jinn</t>
+        </is>
+      </c>
+    </row>
+    <row r="332" ht="24" customHeight="1">
+      <c r="A332" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B332" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="333" ht="24" customHeight="1">
+      <c r="A333" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B333" s="3" t="inlineStr">
+        <is>
+          <t>Qui-Gon Jinn</t>
+        </is>
+      </c>
+    </row>
+    <row r="334" ht="24" customHeight="1">
+      <c r="A334" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B334" s="4" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="335" ht="24" customHeight="1">
+      <c r="A335" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B335" s="3" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+    </row>
+    <row r="336" ht="24" customHeight="1">
+      <c r="A336" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B336" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="337" ht="24" customHeight="1">
+      <c r="A337" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B337" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="338" ht="24" customHeight="1">
+      <c r="A338" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B338" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="339" ht="24" customHeight="1">
+      <c r="A339" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B339" s="3" t="inlineStr">
+        <is>
+          <t>92BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="340" ht="24" customHeight="1">
+      <c r="A340" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B340" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="342" ht="24" customHeight="1">
+      <c r="A342" s="1" t="inlineStr">
+        <is>
+          <t>Nute Gunray</t>
+        </is>
+      </c>
+    </row>
+    <row r="343" ht="24" customHeight="1">
+      <c r="A343" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B343" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="344" ht="24" customHeight="1">
+      <c r="A344" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B344" s="3" t="inlineStr">
+        <is>
+          <t>Nute Gunray</t>
+        </is>
+      </c>
+    </row>
+    <row r="345" ht="24" customHeight="1">
+      <c r="A345" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B345" s="4" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+    </row>
+    <row r="346" ht="24" customHeight="1">
+      <c r="A346" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B346" s="3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+    </row>
+    <row r="347" ht="24" customHeight="1">
+      <c r="A347" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B347" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="348" ht="24" customHeight="1">
+      <c r="A348" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B348" s="3" t="inlineStr">
+        <is>
+          <t>mottled green</t>
+        </is>
+      </c>
+    </row>
+    <row r="349" ht="24" customHeight="1">
+      <c r="A349" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B349" s="4" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="350" ht="24" customHeight="1">
+      <c r="A350" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B350" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="351" ht="24" customHeight="1">
+      <c r="A351" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B351" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="353" ht="24" customHeight="1">
+      <c r="A353" s="1" t="inlineStr">
+        <is>
+          <t>Finis Valorum</t>
+        </is>
+      </c>
+    </row>
+    <row r="354" ht="24" customHeight="1">
+      <c r="A354" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B354" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="355" ht="24" customHeight="1">
+      <c r="A355" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B355" s="3" t="inlineStr">
+        <is>
+          <t>Finis Valorum</t>
+        </is>
+      </c>
+    </row>
+    <row r="356" ht="24" customHeight="1">
+      <c r="A356" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B356" s="4" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="357" ht="24" customHeight="1">
+      <c r="A357" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B357" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="358" ht="24" customHeight="1">
+      <c r="A358" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B358" s="4" t="inlineStr">
+        <is>
+          <t>blond</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="24" customHeight="1">
+      <c r="A359" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B359" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="360" ht="24" customHeight="1">
+      <c r="A360" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B360" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="361" ht="24" customHeight="1">
+      <c r="A361" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B361" s="3" t="inlineStr">
+        <is>
+          <t>91BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="362" ht="24" customHeight="1">
+      <c r="A362" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B362" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="364" ht="24" customHeight="1">
+      <c r="A364" s="1" t="inlineStr">
+        <is>
+          <t>Padmé Amidala</t>
+        </is>
+      </c>
+    </row>
+    <row r="365" ht="24" customHeight="1">
+      <c r="A365" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B365" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="366" ht="24" customHeight="1">
+      <c r="A366" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B366" s="3" t="inlineStr">
+        <is>
+          <t>Padmé Amidala</t>
+        </is>
+      </c>
+    </row>
+    <row r="367" ht="24" customHeight="1">
+      <c r="A367" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B367" s="4" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+    </row>
+    <row r="368" ht="24" customHeight="1">
+      <c r="A368" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B368" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="369" ht="24" customHeight="1">
+      <c r="A369" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B369" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="370" ht="24" customHeight="1">
+      <c r="A370" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B370" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="371" ht="24" customHeight="1">
+      <c r="A371" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B371" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="372" ht="24" customHeight="1">
+      <c r="A372" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B372" s="3" t="inlineStr">
+        <is>
+          <t>46BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="373" ht="24" customHeight="1">
+      <c r="A373" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B373" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="375" ht="24" customHeight="1">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>Jar Jar Binks</t>
+        </is>
+      </c>
+    </row>
+    <row r="376" ht="24" customHeight="1">
+      <c r="A376" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B376" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="377" ht="24" customHeight="1">
+      <c r="A377" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B377" s="3" t="inlineStr">
+        <is>
+          <t>Jar Jar Binks</t>
+        </is>
+      </c>
+    </row>
+    <row r="378" ht="24" customHeight="1">
+      <c r="A378" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B378" s="4" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+    </row>
+    <row r="379" ht="24" customHeight="1">
+      <c r="A379" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B379" s="3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+    </row>
+    <row r="380" ht="24" customHeight="1">
+      <c r="A380" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B380" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="381" ht="24" customHeight="1">
+      <c r="A381" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B381" s="3" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="382" ht="24" customHeight="1">
+      <c r="A382" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B382" s="4" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="383" ht="24" customHeight="1">
+      <c r="A383" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B383" s="3" t="inlineStr">
+        <is>
+          <t>52BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="384" ht="24" customHeight="1">
+      <c r="A384" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B384" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="386" ht="24" customHeight="1">
+      <c r="A386" s="1" t="inlineStr">
+        <is>
+          <t>Roos Tarpals</t>
+        </is>
+      </c>
+    </row>
+    <row r="387" ht="24" customHeight="1">
+      <c r="A387" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B387" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="388" ht="24" customHeight="1">
+      <c r="A388" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B388" s="3" t="inlineStr">
+        <is>
+          <t>Roos Tarpals</t>
+        </is>
+      </c>
+    </row>
+    <row r="389" ht="24" customHeight="1">
+      <c r="A389" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B389" s="4" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+    </row>
+    <row r="390" ht="24" customHeight="1">
+      <c r="A390" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B390" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
+    <row r="391" ht="24" customHeight="1">
+      <c r="A391" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B391" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="392" ht="24" customHeight="1">
+      <c r="A392" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B392" s="3" t="inlineStr">
+        <is>
+          <t>grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="393" ht="24" customHeight="1">
+      <c r="A393" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B393" s="4" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="394" ht="24" customHeight="1">
+      <c r="A394" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B394" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="395" ht="24" customHeight="1">
+      <c r="A395" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B395" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="397" ht="24" customHeight="1">
+      <c r="A397" s="1" t="inlineStr">
+        <is>
+          <t>Rugor Nass</t>
+        </is>
+      </c>
+    </row>
+    <row r="398" ht="24" customHeight="1">
+      <c r="A398" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B398" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="399" ht="24" customHeight="1">
+      <c r="A399" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B399" s="3" t="inlineStr">
+        <is>
+          <t>Rugor Nass</t>
+        </is>
+      </c>
+    </row>
+    <row r="400" ht="24" customHeight="1">
+      <c r="A400" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B400" s="4" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+    </row>
+    <row r="401" ht="24" customHeight="1">
+      <c r="A401" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B401" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="402" ht="24" customHeight="1">
+      <c r="A402" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B402" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="403" ht="24" customHeight="1">
+      <c r="A403" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B403" s="3" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="404" ht="24" customHeight="1">
+      <c r="A404" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B404" s="4" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="405" ht="24" customHeight="1">
+      <c r="A405" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B405" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="406" ht="24" customHeight="1">
+      <c r="A406" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B406" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="408" ht="24" customHeight="1">
+      <c r="A408" s="1" t="inlineStr">
+        <is>
+          <t>Ric Olié</t>
+        </is>
+      </c>
+    </row>
+    <row r="409" ht="24" customHeight="1">
+      <c r="A409" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B409" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="410" ht="24" customHeight="1">
+      <c r="A410" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B410" s="3" t="inlineStr">
+        <is>
+          <t>Ric Olié</t>
+        </is>
+      </c>
+    </row>
+    <row r="411" ht="24" customHeight="1">
+      <c r="A411" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B411" s="4" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="412" ht="24" customHeight="1">
+      <c r="A412" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B412" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="413" ht="24" customHeight="1">
+      <c r="A413" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B413" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="414" ht="24" customHeight="1">
+      <c r="A414" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B414" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="415" ht="24" customHeight="1">
+      <c r="A415" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B415" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="416" ht="24" customHeight="1">
+      <c r="A416" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B416" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="417" ht="24" customHeight="1">
+      <c r="A417" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B417" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="419" ht="24" customHeight="1">
+      <c r="A419" s="1" t="inlineStr">
+        <is>
+          <t>Watto</t>
+        </is>
+      </c>
+    </row>
+    <row r="420" ht="24" customHeight="1">
+      <c r="A420" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B420" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="421" ht="24" customHeight="1">
+      <c r="A421" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B421" s="3" t="inlineStr">
+        <is>
+          <t>Watto</t>
+        </is>
+      </c>
+    </row>
+    <row r="422" ht="24" customHeight="1">
+      <c r="A422" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B422" s="4" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+    </row>
+    <row r="423" ht="24" customHeight="1">
+      <c r="A423" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B423" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="424" ht="24" customHeight="1">
+      <c r="A424" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B424" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="425" ht="24" customHeight="1">
+      <c r="A425" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B425" s="3" t="inlineStr">
+        <is>
+          <t>blue, grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="426" ht="24" customHeight="1">
+      <c r="A426" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B426" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="427" ht="24" customHeight="1">
+      <c r="A427" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B427" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="428" ht="24" customHeight="1">
+      <c r="A428" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B428" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="430" ht="24" customHeight="1">
+      <c r="A430" s="1" t="inlineStr">
+        <is>
+          <t>Sebulba</t>
+        </is>
+      </c>
+    </row>
+    <row r="431" ht="24" customHeight="1">
+      <c r="A431" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B431" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="432" ht="24" customHeight="1">
+      <c r="A432" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B432" s="3" t="inlineStr">
+        <is>
+          <t>Sebulba</t>
+        </is>
+      </c>
+    </row>
+    <row r="433" ht="24" customHeight="1">
+      <c r="A433" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B433" s="4" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+    </row>
+    <row r="434" ht="24" customHeight="1">
+      <c r="A434" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B434" s="3" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+    </row>
+    <row r="435" ht="24" customHeight="1">
+      <c r="A435" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B435" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="436" ht="24" customHeight="1">
+      <c r="A436" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B436" s="3" t="inlineStr">
+        <is>
+          <t>grey, red</t>
+        </is>
+      </c>
+    </row>
+    <row r="437" ht="24" customHeight="1">
+      <c r="A437" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B437" s="4" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="438" ht="24" customHeight="1">
+      <c r="A438" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B438" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="439" ht="24" customHeight="1">
+      <c r="A439" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B439" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="441" ht="24" customHeight="1">
+      <c r="A441" s="1" t="inlineStr">
+        <is>
+          <t>Quarsh Panaka</t>
+        </is>
+      </c>
+    </row>
+    <row r="442" ht="24" customHeight="1">
+      <c r="A442" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B442" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="443" ht="24" customHeight="1">
+      <c r="A443" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B443" s="3" t="inlineStr">
+        <is>
+          <t>Quarsh Panaka</t>
+        </is>
+      </c>
+    </row>
+    <row r="444" ht="24" customHeight="1">
+      <c r="A444" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B444" s="4" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="445" ht="24" customHeight="1">
+      <c r="A445" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B445" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="446" ht="24" customHeight="1">
+      <c r="A446" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B446" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="447" ht="24" customHeight="1">
+      <c r="A447" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B447" s="3" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="448" ht="24" customHeight="1">
+      <c r="A448" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B448" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="449" ht="24" customHeight="1">
+      <c r="A449" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B449" s="3" t="inlineStr">
+        <is>
+          <t>62BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="450" ht="24" customHeight="1">
+      <c r="A450" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B450" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="452" ht="24" customHeight="1">
+      <c r="A452" s="1" t="inlineStr">
+        <is>
+          <t>Shmi Skywalker</t>
+        </is>
+      </c>
+    </row>
+    <row r="453" ht="24" customHeight="1">
+      <c r="A453" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B453" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="454" ht="24" customHeight="1">
+      <c r="A454" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B454" s="3" t="inlineStr">
+        <is>
+          <t>Shmi Skywalker</t>
+        </is>
+      </c>
+    </row>
+    <row r="455" ht="24" customHeight="1">
+      <c r="A455" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B455" s="4" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="456" ht="24" customHeight="1">
+      <c r="A456" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B456" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="457" ht="24" customHeight="1">
+      <c r="A457" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B457" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="458" ht="24" customHeight="1">
+      <c r="A458" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B458" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="459" ht="24" customHeight="1">
+      <c r="A459" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B459" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="460" ht="24" customHeight="1">
+      <c r="A460" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B460" s="3" t="inlineStr">
+        <is>
+          <t>72BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="461" ht="24" customHeight="1">
+      <c r="A461" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B461" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="463" ht="24" customHeight="1">
+      <c r="A463" s="1" t="inlineStr">
+        <is>
+          <t>Darth Maul</t>
+        </is>
+      </c>
+    </row>
+    <row r="464" ht="24" customHeight="1">
+      <c r="A464" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B464" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="465" ht="24" customHeight="1">
+      <c r="A465" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B465" s="3" t="inlineStr">
+        <is>
+          <t>Darth Maul</t>
+        </is>
+      </c>
+    </row>
+    <row r="466" ht="24" customHeight="1">
+      <c r="A466" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B466" s="4" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+    </row>
+    <row r="467" ht="24" customHeight="1">
+      <c r="A467" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B467" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="468" ht="24" customHeight="1">
+      <c r="A468" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B468" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="469" ht="24" customHeight="1">
+      <c r="A469" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B469" s="3" t="inlineStr">
+        <is>
+          <t>red</t>
+        </is>
+      </c>
+    </row>
+    <row r="470" ht="24" customHeight="1">
+      <c r="A470" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B470" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="471" ht="24" customHeight="1">
+      <c r="A471" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B471" s="3" t="inlineStr">
+        <is>
+          <t>54BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="472" ht="24" customHeight="1">
+      <c r="A472" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B472" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="474" ht="24" customHeight="1">
+      <c r="A474" s="1" t="inlineStr">
+        <is>
+          <t>Bib Fortuna</t>
+        </is>
+      </c>
+    </row>
+    <row r="475" ht="24" customHeight="1">
+      <c r="A475" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B475" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="476" ht="24" customHeight="1">
+      <c r="A476" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B476" s="3" t="inlineStr">
+        <is>
+          <t>Bib Fortuna</t>
+        </is>
+      </c>
+    </row>
+    <row r="477" ht="24" customHeight="1">
+      <c r="A477" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B477" s="4" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+    </row>
+    <row r="478" ht="24" customHeight="1">
+      <c r="A478" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B478" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="479" ht="24" customHeight="1">
+      <c r="A479" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B479" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="480" ht="24" customHeight="1">
+      <c r="A480" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B480" s="3" t="inlineStr">
+        <is>
+          <t>pale</t>
+        </is>
+      </c>
+    </row>
+    <row r="481" ht="24" customHeight="1">
+      <c r="A481" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B481" s="4" t="inlineStr">
+        <is>
+          <t>pink</t>
+        </is>
+      </c>
+    </row>
+    <row r="482" ht="24" customHeight="1">
+      <c r="A482" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B482" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="483" ht="24" customHeight="1">
+      <c r="A483" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B483" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="485" ht="24" customHeight="1">
+      <c r="A485" s="1" t="inlineStr">
+        <is>
+          <t>Ayla Secura</t>
+        </is>
+      </c>
+    </row>
+    <row r="486" ht="24" customHeight="1">
+      <c r="A486" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B486" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="487" ht="24" customHeight="1">
+      <c r="A487" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B487" s="3" t="inlineStr">
+        <is>
+          <t>Ayla Secura</t>
+        </is>
+      </c>
+    </row>
+    <row r="488" ht="24" customHeight="1">
+      <c r="A488" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B488" s="4" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="489" ht="24" customHeight="1">
+      <c r="A489" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B489" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="490" ht="24" customHeight="1">
+      <c r="A490" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B490" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="491" ht="24" customHeight="1">
+      <c r="A491" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B491" s="3" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="492" ht="24" customHeight="1">
+      <c r="A492" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B492" s="4" t="inlineStr">
+        <is>
+          <t>hazel</t>
+        </is>
+      </c>
+    </row>
+    <row r="493" ht="24" customHeight="1">
+      <c r="A493" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B493" s="3" t="inlineStr">
+        <is>
+          <t>48BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="494" ht="24" customHeight="1">
+      <c r="A494" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B494" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="496" ht="24" customHeight="1">
+      <c r="A496" s="1" t="inlineStr">
+        <is>
+          <t>Ratts Tyerel</t>
+        </is>
+      </c>
+    </row>
+    <row r="497" ht="24" customHeight="1">
+      <c r="A497" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B497" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="498" ht="24" customHeight="1">
+      <c r="A498" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B498" s="3" t="inlineStr">
+        <is>
+          <t>Ratts Tyerel</t>
+        </is>
+      </c>
+    </row>
+    <row r="499" ht="24" customHeight="1">
+      <c r="A499" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B499" s="4" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="500" ht="24" customHeight="1">
+      <c r="A500" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B500" s="3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+    </row>
+    <row r="501" ht="24" customHeight="1">
+      <c r="A501" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B501" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="502" ht="24" customHeight="1">
+      <c r="A502" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B502" s="3" t="inlineStr">
+        <is>
+          <t>grey, blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="503" ht="24" customHeight="1">
+      <c r="A503" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B503" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="504" ht="24" customHeight="1">
+      <c r="A504" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B504" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="505" ht="24" customHeight="1">
+      <c r="A505" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B505" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="507" ht="24" customHeight="1">
+      <c r="A507" s="1" t="inlineStr">
+        <is>
+          <t>Dud Bolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="508" ht="24" customHeight="1">
+      <c r="A508" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B508" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="509" ht="24" customHeight="1">
+      <c r="A509" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B509" s="3" t="inlineStr">
+        <is>
+          <t>Dud Bolt</t>
+        </is>
+      </c>
+    </row>
+    <row r="510" ht="24" customHeight="1">
+      <c r="A510" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B510" s="4" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+    </row>
+    <row r="511" ht="24" customHeight="1">
+      <c r="A511" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B511" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+    </row>
+    <row r="512" ht="24" customHeight="1">
+      <c r="A512" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B512" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="513" ht="24" customHeight="1">
+      <c r="A513" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B513" s="3" t="inlineStr">
+        <is>
+          <t>blue, grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="514" ht="24" customHeight="1">
+      <c r="A514" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B514" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="515" ht="24" customHeight="1">
+      <c r="A515" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B515" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="516" ht="24" customHeight="1">
+      <c r="A516" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B516" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="518" ht="24" customHeight="1">
+      <c r="A518" s="1" t="inlineStr">
+        <is>
+          <t>Gasgano</t>
+        </is>
+      </c>
+    </row>
+    <row r="519" ht="24" customHeight="1">
+      <c r="A519" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B519" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="520" ht="24" customHeight="1">
+      <c r="A520" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B520" s="3" t="inlineStr">
+        <is>
+          <t>Gasgano</t>
+        </is>
+      </c>
+    </row>
+    <row r="521" ht="24" customHeight="1">
+      <c r="A521" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B521" s="4" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+    </row>
+    <row r="522" ht="24" customHeight="1">
+      <c r="A522" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B522" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="523" ht="24" customHeight="1">
+      <c r="A523" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B523" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="524" ht="24" customHeight="1">
+      <c r="A524" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B524" s="3" t="inlineStr">
+        <is>
+          <t>white, blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="525" ht="24" customHeight="1">
+      <c r="A525" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B525" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="526" ht="24" customHeight="1">
+      <c r="A526" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B526" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="527" ht="24" customHeight="1">
+      <c r="A527" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B527" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="529" ht="24" customHeight="1">
+      <c r="A529" s="1" t="inlineStr">
+        <is>
+          <t>Ben Quadinaros</t>
+        </is>
+      </c>
+    </row>
+    <row r="530" ht="24" customHeight="1">
+      <c r="A530" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B530" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="531" ht="24" customHeight="1">
+      <c r="A531" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B531" s="3" t="inlineStr">
+        <is>
+          <t>Ben Quadinaros</t>
+        </is>
+      </c>
+    </row>
+    <row r="532" ht="24" customHeight="1">
+      <c r="A532" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B532" s="4" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+    </row>
+    <row r="533" ht="24" customHeight="1">
+      <c r="A533" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B533" s="3" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="534" ht="24" customHeight="1">
+      <c r="A534" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B534" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="535" ht="24" customHeight="1">
+      <c r="A535" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B535" s="3" t="inlineStr">
+        <is>
+          <t>grey, green, yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="536" ht="24" customHeight="1">
+      <c r="A536" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B536" s="4" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="537" ht="24" customHeight="1">
+      <c r="A537" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B537" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="538" ht="24" customHeight="1">
+      <c r="A538" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B538" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="540" ht="24" customHeight="1">
+      <c r="A540" s="1" t="inlineStr">
+        <is>
+          <t>Mace Windu</t>
+        </is>
+      </c>
+    </row>
+    <row r="541" ht="24" customHeight="1">
+      <c r="A541" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B541" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="542" ht="24" customHeight="1">
+      <c r="A542" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B542" s="3" t="inlineStr">
+        <is>
+          <t>Mace Windu</t>
+        </is>
+      </c>
+    </row>
+    <row r="543" ht="24" customHeight="1">
+      <c r="A543" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B543" s="4" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="544" ht="24" customHeight="1">
+      <c r="A544" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B544" s="3" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+    </row>
+    <row r="545" ht="24" customHeight="1">
+      <c r="A545" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B545" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="546" ht="24" customHeight="1">
+      <c r="A546" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B546" s="3" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="547" ht="24" customHeight="1">
+      <c r="A547" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B547" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="548" ht="24" customHeight="1">
+      <c r="A548" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B548" s="3" t="inlineStr">
+        <is>
+          <t>72BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="549" ht="24" customHeight="1">
+      <c r="A549" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B549" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="551" ht="24" customHeight="1">
+      <c r="A551" s="1" t="inlineStr">
+        <is>
+          <t>Ki-Adi-Mundi</t>
+        </is>
+      </c>
+    </row>
+    <row r="552" ht="24" customHeight="1">
+      <c r="A552" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B552" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="553" ht="24" customHeight="1">
+      <c r="A553" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B553" s="3" t="inlineStr">
+        <is>
+          <t>Ki-Adi-Mundi</t>
+        </is>
+      </c>
+    </row>
+    <row r="554" ht="24" customHeight="1">
+      <c r="A554" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B554" s="4" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+    </row>
+    <row r="555" ht="24" customHeight="1">
+      <c r="A555" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B555" s="3" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+    </row>
+    <row r="556" ht="24" customHeight="1">
+      <c r="A556" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B556" s="4" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+    </row>
+    <row r="557" ht="24" customHeight="1">
+      <c r="A557" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B557" s="3" t="inlineStr">
+        <is>
+          <t>pale</t>
+        </is>
+      </c>
+    </row>
+    <row r="558" ht="24" customHeight="1">
+      <c r="A558" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B558" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="559" ht="24" customHeight="1">
+      <c r="A559" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B559" s="3" t="inlineStr">
+        <is>
+          <t>92BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="560" ht="24" customHeight="1">
+      <c r="A560" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B560" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="562" ht="24" customHeight="1">
+      <c r="A562" s="1" t="inlineStr">
+        <is>
+          <t>Kit Fisto</t>
+        </is>
+      </c>
+    </row>
+    <row r="563" ht="24" customHeight="1">
+      <c r="A563" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B563" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="564" ht="24" customHeight="1">
+      <c r="A564" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B564" s="3" t="inlineStr">
+        <is>
+          <t>Kit Fisto</t>
+        </is>
+      </c>
+    </row>
+    <row r="565" ht="24" customHeight="1">
+      <c r="A565" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B565" s="4" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+    </row>
+    <row r="566" ht="24" customHeight="1">
+      <c r="A566" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B566" s="3" t="inlineStr">
+        <is>
+          <t>87</t>
+        </is>
+      </c>
+    </row>
+    <row r="567" ht="24" customHeight="1">
+      <c r="A567" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B567" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="568" ht="24" customHeight="1">
+      <c r="A568" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B568" s="3" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="569" ht="24" customHeight="1">
+      <c r="A569" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B569" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="570" ht="24" customHeight="1">
+      <c r="A570" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B570" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="571" ht="24" customHeight="1">
+      <c r="A571" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B571" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="573" ht="24" customHeight="1">
+      <c r="A573" s="1" t="inlineStr">
+        <is>
+          <t>Eeth Koth</t>
+        </is>
+      </c>
+    </row>
+    <row r="574" ht="24" customHeight="1">
+      <c r="A574" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B574" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="575" ht="24" customHeight="1">
+      <c r="A575" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B575" s="3" t="inlineStr">
+        <is>
+          <t>Eeth Koth</t>
+        </is>
+      </c>
+    </row>
+    <row r="576" ht="24" customHeight="1">
+      <c r="A576" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B576" s="4" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+    </row>
+    <row r="577" ht="24" customHeight="1">
+      <c r="A577" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B577" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="578" ht="24" customHeight="1">
+      <c r="A578" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B578" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="579" ht="24" customHeight="1">
+      <c r="A579" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B579" s="3" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="580" ht="24" customHeight="1">
+      <c r="A580" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B580" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="581" ht="24" customHeight="1">
+      <c r="A581" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B581" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="582" ht="24" customHeight="1">
+      <c r="A582" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B582" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="584" ht="24" customHeight="1">
+      <c r="A584" s="1" t="inlineStr">
+        <is>
+          <t>Adi Gallia</t>
+        </is>
+      </c>
+    </row>
+    <row r="585" ht="24" customHeight="1">
+      <c r="A585" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B585" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="586" ht="24" customHeight="1">
+      <c r="A586" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B586" s="3" t="inlineStr">
+        <is>
+          <t>Adi Gallia</t>
+        </is>
+      </c>
+    </row>
+    <row r="587" ht="24" customHeight="1">
+      <c r="A587" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B587" s="4" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+    </row>
+    <row r="588" ht="24" customHeight="1">
+      <c r="A588" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B588" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="589" ht="24" customHeight="1">
+      <c r="A589" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B589" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="590" ht="24" customHeight="1">
+      <c r="A590" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B590" s="3" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="591" ht="24" customHeight="1">
+      <c r="A591" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B591" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="592" ht="24" customHeight="1">
+      <c r="A592" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B592" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="593" ht="24" customHeight="1">
+      <c r="A593" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B593" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="595" ht="24" customHeight="1">
+      <c r="A595" s="1" t="inlineStr">
+        <is>
+          <t>Saesee Tiin</t>
+        </is>
+      </c>
+    </row>
+    <row r="596" ht="24" customHeight="1">
+      <c r="A596" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B596" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="597" ht="24" customHeight="1">
+      <c r="A597" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B597" s="3" t="inlineStr">
+        <is>
+          <t>Saesee Tiin</t>
+        </is>
+      </c>
+    </row>
+    <row r="598" ht="24" customHeight="1">
+      <c r="A598" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B598" s="4" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="599" ht="24" customHeight="1">
+      <c r="A599" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B599" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="600" ht="24" customHeight="1">
+      <c r="A600" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B600" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="601" ht="24" customHeight="1">
+      <c r="A601" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B601" s="3" t="inlineStr">
+        <is>
+          <t>pale</t>
+        </is>
+      </c>
+    </row>
+    <row r="602" ht="24" customHeight="1">
+      <c r="A602" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B602" s="4" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="603" ht="24" customHeight="1">
+      <c r="A603" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B603" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="604" ht="24" customHeight="1">
+      <c r="A604" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B604" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="606" ht="24" customHeight="1">
+      <c r="A606" s="1" t="inlineStr">
+        <is>
+          <t>Yarael Poof</t>
+        </is>
+      </c>
+    </row>
+    <row r="607" ht="24" customHeight="1">
+      <c r="A607" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B607" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="608" ht="24" customHeight="1">
+      <c r="A608" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B608" s="3" t="inlineStr">
+        <is>
+          <t>Yarael Poof</t>
+        </is>
+      </c>
+    </row>
+    <row r="609" ht="24" customHeight="1">
+      <c r="A609" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B609" s="4" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+    </row>
+    <row r="610" ht="24" customHeight="1">
+      <c r="A610" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B610" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="611" ht="24" customHeight="1">
+      <c r="A611" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B611" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="612" ht="24" customHeight="1">
+      <c r="A612" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B612" s="3" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+    </row>
+    <row r="613" ht="24" customHeight="1">
+      <c r="A613" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B613" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="614" ht="24" customHeight="1">
+      <c r="A614" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B614" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="615" ht="24" customHeight="1">
+      <c r="A615" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B615" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="617" ht="24" customHeight="1">
+      <c r="A617" s="1" t="inlineStr">
+        <is>
+          <t>Plo Koon</t>
+        </is>
+      </c>
+    </row>
+    <row r="618" ht="24" customHeight="1">
+      <c r="A618" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B618" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="619" ht="24" customHeight="1">
+      <c r="A619" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B619" s="3" t="inlineStr">
+        <is>
+          <t>Plo Koon</t>
+        </is>
+      </c>
+    </row>
+    <row r="620" ht="24" customHeight="1">
+      <c r="A620" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B620" s="4" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="621" ht="24" customHeight="1">
+      <c r="A621" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B621" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="622" ht="24" customHeight="1">
+      <c r="A622" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B622" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="623" ht="24" customHeight="1">
+      <c r="A623" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B623" s="3" t="inlineStr">
+        <is>
+          <t>orange</t>
+        </is>
+      </c>
+    </row>
+    <row r="624" ht="24" customHeight="1">
+      <c r="A624" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B624" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="625" ht="24" customHeight="1">
+      <c r="A625" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B625" s="3" t="inlineStr">
+        <is>
+          <t>22BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="626" ht="24" customHeight="1">
+      <c r="A626" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B626" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="628" ht="24" customHeight="1">
+      <c r="A628" s="1" t="inlineStr">
+        <is>
+          <t>Mas Amedda</t>
+        </is>
+      </c>
+    </row>
+    <row r="629" ht="24" customHeight="1">
+      <c r="A629" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B629" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="630" ht="24" customHeight="1">
+      <c r="A630" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B630" s="3" t="inlineStr">
+        <is>
+          <t>Mas Amedda</t>
+        </is>
+      </c>
+    </row>
+    <row r="631" ht="24" customHeight="1">
+      <c r="A631" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B631" s="4" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+    </row>
+    <row r="632" ht="24" customHeight="1">
+      <c r="A632" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B632" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="633" ht="24" customHeight="1">
+      <c r="A633" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B633" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="634" ht="24" customHeight="1">
+      <c r="A634" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B634" s="3" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="635" ht="24" customHeight="1">
+      <c r="A635" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B635" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="636" ht="24" customHeight="1">
+      <c r="A636" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B636" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="637" ht="24" customHeight="1">
+      <c r="A637" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B637" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="639" ht="24" customHeight="1">
+      <c r="A639" s="1" t="inlineStr">
+        <is>
+          <t>Gregar Typho</t>
+        </is>
+      </c>
+    </row>
+    <row r="640" ht="24" customHeight="1">
+      <c r="A640" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B640" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="641" ht="24" customHeight="1">
+      <c r="A641" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B641" s="3" t="inlineStr">
+        <is>
+          <t>Gregar Typho</t>
+        </is>
+      </c>
+    </row>
+    <row r="642" ht="24" customHeight="1">
+      <c r="A642" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B642" s="4" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+    </row>
+    <row r="643" ht="24" customHeight="1">
+      <c r="A643" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B643" s="3" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+    </row>
+    <row r="644" ht="24" customHeight="1">
+      <c r="A644" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B644" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="645" ht="24" customHeight="1">
+      <c r="A645" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B645" s="3" t="inlineStr">
+        <is>
+          <t>dark</t>
+        </is>
+      </c>
+    </row>
+    <row r="646" ht="24" customHeight="1">
+      <c r="A646" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B646" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="647" ht="24" customHeight="1">
+      <c r="A647" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B647" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="648" ht="24" customHeight="1">
+      <c r="A648" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B648" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="650" ht="24" customHeight="1">
+      <c r="A650" s="1" t="inlineStr">
+        <is>
+          <t>Cordé</t>
+        </is>
+      </c>
+    </row>
+    <row r="651" ht="24" customHeight="1">
+      <c r="A651" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B651" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="652" ht="24" customHeight="1">
+      <c r="A652" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B652" s="3" t="inlineStr">
+        <is>
+          <t>Cordé</t>
+        </is>
+      </c>
+    </row>
+    <row r="653" ht="24" customHeight="1">
+      <c r="A653" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B653" s="4" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+    </row>
+    <row r="654" ht="24" customHeight="1">
+      <c r="A654" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B654" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="655" ht="24" customHeight="1">
+      <c r="A655" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B655" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="656" ht="24" customHeight="1">
+      <c r="A656" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B656" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="657" ht="24" customHeight="1">
+      <c r="A657" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B657" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="658" ht="24" customHeight="1">
+      <c r="A658" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B658" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="659" ht="24" customHeight="1">
+      <c r="A659" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B659" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="661" ht="24" customHeight="1">
+      <c r="A661" s="1" t="inlineStr">
+        <is>
+          <t>Cliegg Lars</t>
+        </is>
+      </c>
+    </row>
+    <row r="662" ht="24" customHeight="1">
+      <c r="A662" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B662" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="663" ht="24" customHeight="1">
+      <c r="A663" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B663" s="3" t="inlineStr">
+        <is>
+          <t>Cliegg Lars</t>
+        </is>
+      </c>
+    </row>
+    <row r="664" ht="24" customHeight="1">
+      <c r="A664" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B664" s="4" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="665" ht="24" customHeight="1">
+      <c r="A665" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B665" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="666" ht="24" customHeight="1">
+      <c r="A666" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B666" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="667" ht="24" customHeight="1">
+      <c r="A667" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B667" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="668" ht="24" customHeight="1">
+      <c r="A668" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B668" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="669" ht="24" customHeight="1">
+      <c r="A669" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B669" s="3" t="inlineStr">
+        <is>
+          <t>82BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="670" ht="24" customHeight="1">
+      <c r="A670" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B670" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="672" ht="24" customHeight="1">
+      <c r="A672" s="1" t="inlineStr">
+        <is>
+          <t>Poggle the Lesser</t>
+        </is>
+      </c>
+    </row>
+    <row r="673" ht="24" customHeight="1">
+      <c r="A673" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B673" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="674" ht="24" customHeight="1">
+      <c r="A674" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B674" s="3" t="inlineStr">
+        <is>
+          <t>Poggle the Lesser</t>
+        </is>
+      </c>
+    </row>
+    <row r="675" ht="24" customHeight="1">
+      <c r="A675" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B675" s="4" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="676" ht="24" customHeight="1">
+      <c r="A676" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B676" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="677" ht="24" customHeight="1">
+      <c r="A677" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B677" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="678" ht="24" customHeight="1">
+      <c r="A678" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B678" s="3" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+    </row>
+    <row r="679" ht="24" customHeight="1">
+      <c r="A679" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B679" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="680" ht="24" customHeight="1">
+      <c r="A680" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B680" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="681" ht="24" customHeight="1">
+      <c r="A681" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B681" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="683" ht="24" customHeight="1">
+      <c r="A683" s="1" t="inlineStr">
+        <is>
+          <t>Luminara Unduli</t>
+        </is>
+      </c>
+    </row>
+    <row r="684" ht="24" customHeight="1">
+      <c r="A684" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B684" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="685" ht="24" customHeight="1">
+      <c r="A685" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B685" s="3" t="inlineStr">
+        <is>
+          <t>Luminara Unduli</t>
+        </is>
+      </c>
+    </row>
+    <row r="686" ht="24" customHeight="1">
+      <c r="A686" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B686" s="4" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+    </row>
+    <row r="687" ht="24" customHeight="1">
+      <c r="A687" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B687" s="3" t="inlineStr">
+        <is>
+          <t>56.2</t>
+        </is>
+      </c>
+    </row>
+    <row r="688" ht="24" customHeight="1">
+      <c r="A688" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B688" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="689" ht="24" customHeight="1">
+      <c r="A689" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B689" s="3" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="690" ht="24" customHeight="1">
+      <c r="A690" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B690" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="691" ht="24" customHeight="1">
+      <c r="A691" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B691" s="3" t="inlineStr">
+        <is>
+          <t>58BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="692" ht="24" customHeight="1">
+      <c r="A692" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B692" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="694" ht="24" customHeight="1">
+      <c r="A694" s="1" t="inlineStr">
+        <is>
+          <t>Barriss Offee</t>
+        </is>
+      </c>
+    </row>
+    <row r="695" ht="24" customHeight="1">
+      <c r="A695" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B695" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="696" ht="24" customHeight="1">
+      <c r="A696" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B696" s="3" t="inlineStr">
+        <is>
+          <t>Barriss Offee</t>
+        </is>
+      </c>
+    </row>
+    <row r="697" ht="24" customHeight="1">
+      <c r="A697" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B697" s="4" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+    </row>
+    <row r="698" ht="24" customHeight="1">
+      <c r="A698" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B698" s="3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="699" ht="24" customHeight="1">
+      <c r="A699" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B699" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="700" ht="24" customHeight="1">
+      <c r="A700" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B700" s="3" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="701" ht="24" customHeight="1">
+      <c r="A701" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B701" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="702" ht="24" customHeight="1">
+      <c r="A702" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B702" s="3" t="inlineStr">
+        <is>
+          <t>40BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="703" ht="24" customHeight="1">
+      <c r="A703" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B703" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="705" ht="24" customHeight="1">
+      <c r="A705" s="1" t="inlineStr">
+        <is>
+          <t>Dormé</t>
+        </is>
+      </c>
+    </row>
+    <row r="706" ht="24" customHeight="1">
+      <c r="A706" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B706" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="707" ht="24" customHeight="1">
+      <c r="A707" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B707" s="3" t="inlineStr">
+        <is>
+          <t>Dormé</t>
+        </is>
+      </c>
+    </row>
+    <row r="708" ht="24" customHeight="1">
+      <c r="A708" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B708" s="4" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+    </row>
+    <row r="709" ht="24" customHeight="1">
+      <c r="A709" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B709" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="710" ht="24" customHeight="1">
+      <c r="A710" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B710" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="711" ht="24" customHeight="1">
+      <c r="A711" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B711" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="712" ht="24" customHeight="1">
+      <c r="A712" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B712" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="713" ht="24" customHeight="1">
+      <c r="A713" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B713" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="714" ht="24" customHeight="1">
+      <c r="A714" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B714" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="716" ht="24" customHeight="1">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>Dooku</t>
+        </is>
+      </c>
+    </row>
+    <row r="717" ht="24" customHeight="1">
+      <c r="A717" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B717" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="718" ht="24" customHeight="1">
+      <c r="A718" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B718" s="3" t="inlineStr">
+        <is>
+          <t>Dooku</t>
+        </is>
+      </c>
+    </row>
+    <row r="719" ht="24" customHeight="1">
+      <c r="A719" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B719" s="4" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="720" ht="24" customHeight="1">
+      <c r="A720" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B720" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="721" ht="24" customHeight="1">
+      <c r="A721" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B721" s="4" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+    </row>
+    <row r="722" ht="24" customHeight="1">
+      <c r="A722" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B722" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="723" ht="24" customHeight="1">
+      <c r="A723" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B723" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="724" ht="24" customHeight="1">
+      <c r="A724" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B724" s="3" t="inlineStr">
+        <is>
+          <t>102BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="725" ht="24" customHeight="1">
+      <c r="A725" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B725" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="727" ht="24" customHeight="1">
+      <c r="A727" s="1" t="inlineStr">
+        <is>
+          <t>Bail Prestor Organa</t>
+        </is>
+      </c>
+    </row>
+    <row r="728" ht="24" customHeight="1">
+      <c r="A728" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B728" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="729" ht="24" customHeight="1">
+      <c r="A729" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B729" s="3" t="inlineStr">
+        <is>
+          <t>Bail Prestor Organa</t>
+        </is>
+      </c>
+    </row>
+    <row r="730" ht="24" customHeight="1">
+      <c r="A730" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B730" s="4" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+    </row>
+    <row r="731" ht="24" customHeight="1">
+      <c r="A731" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B731" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="732" ht="24" customHeight="1">
+      <c r="A732" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B732" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="733" ht="24" customHeight="1">
+      <c r="A733" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B733" s="3" t="inlineStr">
+        <is>
+          <t>tan</t>
+        </is>
+      </c>
+    </row>
+    <row r="734" ht="24" customHeight="1">
+      <c r="A734" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B734" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="735" ht="24" customHeight="1">
+      <c r="A735" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B735" s="3" t="inlineStr">
+        <is>
+          <t>67BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="736" ht="24" customHeight="1">
+      <c r="A736" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B736" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="738" ht="24" customHeight="1">
+      <c r="A738" s="1" t="inlineStr">
+        <is>
+          <t>Jango Fett</t>
+        </is>
+      </c>
+    </row>
+    <row r="739" ht="24" customHeight="1">
+      <c r="A739" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B739" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="740" ht="24" customHeight="1">
+      <c r="A740" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B740" s="3" t="inlineStr">
+        <is>
+          <t>Jango Fett</t>
+        </is>
+      </c>
+    </row>
+    <row r="741" ht="24" customHeight="1">
+      <c r="A741" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B741" s="4" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+    </row>
+    <row r="742" ht="24" customHeight="1">
+      <c r="A742" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B742" s="3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="743" ht="24" customHeight="1">
+      <c r="A743" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B743" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="744" ht="24" customHeight="1">
+      <c r="A744" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B744" s="3" t="inlineStr">
+        <is>
+          <t>tan</t>
+        </is>
+      </c>
+    </row>
+    <row r="745" ht="24" customHeight="1">
+      <c r="A745" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B745" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="746" ht="24" customHeight="1">
+      <c r="A746" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B746" s="3" t="inlineStr">
+        <is>
+          <t>66BBY</t>
+        </is>
+      </c>
+    </row>
+    <row r="747" ht="24" customHeight="1">
+      <c r="A747" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B747" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="749" ht="24" customHeight="1">
+      <c r="A749" s="1" t="inlineStr">
+        <is>
+          <t>Zam Wesell</t>
+        </is>
+      </c>
+    </row>
+    <row r="750" ht="24" customHeight="1">
+      <c r="A750" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B750" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="751" ht="24" customHeight="1">
+      <c r="A751" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B751" s="3" t="inlineStr">
+        <is>
+          <t>Zam Wesell</t>
+        </is>
+      </c>
+    </row>
+    <row r="752" ht="24" customHeight="1">
+      <c r="A752" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B752" s="4" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+    </row>
+    <row r="753" ht="24" customHeight="1">
+      <c r="A753" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B753" s="3" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+    </row>
+    <row r="754" ht="24" customHeight="1">
+      <c r="A754" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B754" s="4" t="inlineStr">
+        <is>
+          <t>blonde</t>
+        </is>
+      </c>
+    </row>
+    <row r="755" ht="24" customHeight="1">
+      <c r="A755" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B755" s="3" t="inlineStr">
+        <is>
+          <t>fair, green, yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="756" ht="24" customHeight="1">
+      <c r="A756" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B756" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="757" ht="24" customHeight="1">
+      <c r="A757" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B757" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="758" ht="24" customHeight="1">
+      <c r="A758" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B758" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="760" ht="24" customHeight="1">
+      <c r="A760" s="1" t="inlineStr">
+        <is>
+          <t>Dexter Jettster</t>
+        </is>
+      </c>
+    </row>
+    <row r="761" ht="24" customHeight="1">
+      <c r="A761" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B761" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="762" ht="24" customHeight="1">
+      <c r="A762" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B762" s="3" t="inlineStr">
+        <is>
+          <t>Dexter Jettster</t>
+        </is>
+      </c>
+    </row>
+    <row r="763" ht="24" customHeight="1">
+      <c r="A763" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B763" s="4" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+    </row>
+    <row r="764" ht="24" customHeight="1">
+      <c r="A764" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B764" s="3" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+    </row>
+    <row r="765" ht="24" customHeight="1">
+      <c r="A765" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B765" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="766" ht="24" customHeight="1">
+      <c r="A766" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B766" s="3" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="767" ht="24" customHeight="1">
+      <c r="A767" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B767" s="4" t="inlineStr">
+        <is>
+          <t>yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="768" ht="24" customHeight="1">
+      <c r="A768" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B768" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="769" ht="24" customHeight="1">
+      <c r="A769" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B769" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="771" ht="24" customHeight="1">
+      <c r="A771" s="1" t="inlineStr">
+        <is>
+          <t>Lama Su</t>
+        </is>
+      </c>
+    </row>
+    <row r="772" ht="24" customHeight="1">
+      <c r="A772" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B772" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="773" ht="24" customHeight="1">
+      <c r="A773" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B773" s="3" t="inlineStr">
+        <is>
+          <t>Lama Su</t>
+        </is>
+      </c>
+    </row>
+    <row r="774" ht="24" customHeight="1">
+      <c r="A774" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B774" s="4" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+    </row>
+    <row r="775" ht="24" customHeight="1">
+      <c r="A775" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B775" s="3" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+    </row>
+    <row r="776" ht="24" customHeight="1">
+      <c r="A776" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B776" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="777" ht="24" customHeight="1">
+      <c r="A777" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B777" s="3" t="inlineStr">
+        <is>
+          <t>grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="778" ht="24" customHeight="1">
+      <c r="A778" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B778" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="779" ht="24" customHeight="1">
+      <c r="A779" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B779" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="780" ht="24" customHeight="1">
+      <c r="A780" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B780" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="782" ht="24" customHeight="1">
+      <c r="A782" s="1" t="inlineStr">
+        <is>
+          <t>Taun We</t>
+        </is>
+      </c>
+    </row>
+    <row r="783" ht="24" customHeight="1">
+      <c r="A783" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B783" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="784" ht="24" customHeight="1">
+      <c r="A784" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B784" s="3" t="inlineStr">
+        <is>
+          <t>Taun We</t>
+        </is>
+      </c>
+    </row>
+    <row r="785" ht="24" customHeight="1">
+      <c r="A785" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B785" s="4" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+    </row>
+    <row r="786" ht="24" customHeight="1">
+      <c r="A786" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B786" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="787" ht="24" customHeight="1">
+      <c r="A787" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B787" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="788" ht="24" customHeight="1">
+      <c r="A788" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B788" s="3" t="inlineStr">
+        <is>
+          <t>grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="789" ht="24" customHeight="1">
+      <c r="A789" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B789" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="790" ht="24" customHeight="1">
+      <c r="A790" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B790" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="791" ht="24" customHeight="1">
+      <c r="A791" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B791" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="793" ht="24" customHeight="1">
+      <c r="A793" s="1" t="inlineStr">
+        <is>
+          <t>Jocasta Nu</t>
+        </is>
+      </c>
+    </row>
+    <row r="794" ht="24" customHeight="1">
+      <c r="A794" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B794" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="795" ht="24" customHeight="1">
+      <c r="A795" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B795" s="3" t="inlineStr">
+        <is>
+          <t>Jocasta Nu</t>
+        </is>
+      </c>
+    </row>
+    <row r="796" ht="24" customHeight="1">
+      <c r="A796" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B796" s="4" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+    </row>
+    <row r="797" ht="24" customHeight="1">
+      <c r="A797" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B797" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="798" ht="24" customHeight="1">
+      <c r="A798" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B798" s="4" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+    </row>
+    <row r="799" ht="24" customHeight="1">
+      <c r="A799" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B799" s="3" t="inlineStr">
+        <is>
+          <t>fair</t>
+        </is>
+      </c>
+    </row>
+    <row r="800" ht="24" customHeight="1">
+      <c r="A800" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B800" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="801" ht="24" customHeight="1">
+      <c r="A801" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B801" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="802" ht="24" customHeight="1">
+      <c r="A802" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B802" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="804" ht="24" customHeight="1">
+      <c r="A804" s="1" t="inlineStr">
+        <is>
+          <t>R4-P17</t>
+        </is>
+      </c>
+    </row>
+    <row r="805" ht="24" customHeight="1">
+      <c r="A805" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B805" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="806" ht="24" customHeight="1">
+      <c r="A806" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B806" s="3" t="inlineStr">
+        <is>
+          <t>R4-P17</t>
+        </is>
+      </c>
+    </row>
+    <row r="807" ht="24" customHeight="1">
+      <c r="A807" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B807" s="4" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+    </row>
+    <row r="808" ht="24" customHeight="1">
+      <c r="A808" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B808" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="809" ht="24" customHeight="1">
+      <c r="A809" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B809" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="810" ht="24" customHeight="1">
+      <c r="A810" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B810" s="3" t="inlineStr">
+        <is>
+          <t>silver, red</t>
+        </is>
+      </c>
+    </row>
+    <row r="811" ht="24" customHeight="1">
+      <c r="A811" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B811" s="4" t="inlineStr">
+        <is>
+          <t>red, blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="812" ht="24" customHeight="1">
+      <c r="A812" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B812" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="813" ht="24" customHeight="1">
+      <c r="A813" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B813" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="815" ht="24" customHeight="1">
+      <c r="A815" s="1" t="inlineStr">
+        <is>
+          <t>Wat Tambor</t>
+        </is>
+      </c>
+    </row>
+    <row r="816" ht="24" customHeight="1">
+      <c r="A816" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B816" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="817" ht="24" customHeight="1">
+      <c r="A817" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B817" s="3" t="inlineStr">
+        <is>
+          <t>Wat Tambor</t>
+        </is>
+      </c>
+    </row>
+    <row r="818" ht="24" customHeight="1">
+      <c r="A818" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B818" s="4" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+    </row>
+    <row r="819" ht="24" customHeight="1">
+      <c r="A819" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B819" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="820" ht="24" customHeight="1">
+      <c r="A820" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B820" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="821" ht="24" customHeight="1">
+      <c r="A821" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B821" s="3" t="inlineStr">
+        <is>
+          <t>green, grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="822" ht="24" customHeight="1">
+      <c r="A822" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B822" s="4" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="823" ht="24" customHeight="1">
+      <c r="A823" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B823" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="824" ht="24" customHeight="1">
+      <c r="A824" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B824" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="826" ht="24" customHeight="1">
+      <c r="A826" s="1" t="inlineStr">
+        <is>
+          <t>San Hill</t>
+        </is>
+      </c>
+    </row>
+    <row r="827" ht="24" customHeight="1">
+      <c r="A827" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B827" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="828" ht="24" customHeight="1">
+      <c r="A828" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B828" s="3" t="inlineStr">
+        <is>
+          <t>San Hill</t>
+        </is>
+      </c>
+    </row>
+    <row r="829" ht="24" customHeight="1">
+      <c r="A829" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B829" s="4" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+    </row>
+    <row r="830" ht="24" customHeight="1">
+      <c r="A830" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B830" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="831" ht="24" customHeight="1">
+      <c r="A831" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B831" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="832" ht="24" customHeight="1">
+      <c r="A832" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B832" s="3" t="inlineStr">
+        <is>
+          <t>grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="833" ht="24" customHeight="1">
+      <c r="A833" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B833" s="4" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+    </row>
+    <row r="834" ht="24" customHeight="1">
+      <c r="A834" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B834" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="835" ht="24" customHeight="1">
+      <c r="A835" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B835" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="837" ht="24" customHeight="1">
+      <c r="A837" s="1" t="inlineStr">
+        <is>
+          <t>Shaak Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="838" ht="24" customHeight="1">
+      <c r="A838" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B838" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="839" ht="24" customHeight="1">
+      <c r="A839" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B839" s="3" t="inlineStr">
+        <is>
+          <t>Shaak Ti</t>
+        </is>
+      </c>
+    </row>
+    <row r="840" ht="24" customHeight="1">
+      <c r="A840" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B840" s="4" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="841" ht="24" customHeight="1">
+      <c r="A841" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B841" s="3" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+    </row>
+    <row r="842" ht="24" customHeight="1">
+      <c r="A842" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B842" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="843" ht="24" customHeight="1">
+      <c r="A843" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B843" s="3" t="inlineStr">
+        <is>
+          <t>red, blue, white</t>
+        </is>
+      </c>
+    </row>
+    <row r="844" ht="24" customHeight="1">
+      <c r="A844" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B844" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="845" ht="24" customHeight="1">
+      <c r="A845" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B845" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="846" ht="24" customHeight="1">
+      <c r="A846" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B846" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="848" ht="24" customHeight="1">
+      <c r="A848" s="1" t="inlineStr">
+        <is>
+          <t>Grievous</t>
+        </is>
+      </c>
+    </row>
+    <row r="849" ht="24" customHeight="1">
+      <c r="A849" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B849" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="850" ht="24" customHeight="1">
+      <c r="A850" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B850" s="3" t="inlineStr">
+        <is>
+          <t>Grievous</t>
+        </is>
+      </c>
+    </row>
+    <row r="851" ht="24" customHeight="1">
+      <c r="A851" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B851" s="4" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+    </row>
+    <row r="852" ht="24" customHeight="1">
+      <c r="A852" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B852" s="3" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+    </row>
+    <row r="853" ht="24" customHeight="1">
+      <c r="A853" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B853" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="854" ht="24" customHeight="1">
+      <c r="A854" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B854" s="3" t="inlineStr">
+        <is>
+          <t>brown, white</t>
+        </is>
+      </c>
+    </row>
+    <row r="855" ht="24" customHeight="1">
+      <c r="A855" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B855" s="4" t="inlineStr">
+        <is>
+          <t>green, yellow</t>
+        </is>
+      </c>
+    </row>
+    <row r="856" ht="24" customHeight="1">
+      <c r="A856" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B856" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="857" ht="24" customHeight="1">
+      <c r="A857" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B857" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="859" ht="24" customHeight="1">
+      <c r="A859" s="1" t="inlineStr">
+        <is>
+          <t>Tarfful</t>
+        </is>
+      </c>
+    </row>
+    <row r="860" ht="24" customHeight="1">
+      <c r="A860" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B860" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="861" ht="24" customHeight="1">
+      <c r="A861" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B861" s="3" t="inlineStr">
+        <is>
+          <t>Tarfful</t>
+        </is>
+      </c>
+    </row>
+    <row r="862" ht="24" customHeight="1">
+      <c r="A862" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B862" s="4" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+    </row>
+    <row r="863" ht="24" customHeight="1">
+      <c r="A863" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B863" s="3" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+    </row>
+    <row r="864" ht="24" customHeight="1">
+      <c r="A864" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B864" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="865" ht="24" customHeight="1">
+      <c r="A865" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B865" s="3" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="866" ht="24" customHeight="1">
+      <c r="A866" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B866" s="4" t="inlineStr">
+        <is>
+          <t>blue</t>
+        </is>
+      </c>
+    </row>
+    <row r="867" ht="24" customHeight="1">
+      <c r="A867" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B867" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="868" ht="24" customHeight="1">
+      <c r="A868" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B868" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="870" ht="24" customHeight="1">
+      <c r="A870" s="1" t="inlineStr">
+        <is>
+          <t>Raymus Antilles</t>
+        </is>
+      </c>
+    </row>
+    <row r="871" ht="24" customHeight="1">
+      <c r="A871" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B871" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="872" ht="24" customHeight="1">
+      <c r="A872" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B872" s="3" t="inlineStr">
+        <is>
+          <t>Raymus Antilles</t>
+        </is>
+      </c>
+    </row>
+    <row r="873" ht="24" customHeight="1">
+      <c r="A873" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B873" s="4" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+    </row>
+    <row r="874" ht="24" customHeight="1">
+      <c r="A874" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B874" s="3" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+    </row>
+    <row r="875" ht="24" customHeight="1">
+      <c r="A875" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B875" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="876" ht="24" customHeight="1">
+      <c r="A876" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B876" s="3" t="inlineStr">
+        <is>
+          <t>light</t>
+        </is>
+      </c>
+    </row>
+    <row r="877" ht="24" customHeight="1">
+      <c r="A877" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B877" s="4" t="inlineStr">
+        <is>
+          <t>brown</t>
+        </is>
+      </c>
+    </row>
+    <row r="878" ht="24" customHeight="1">
+      <c r="A878" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B878" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="879" ht="24" customHeight="1">
+      <c r="A879" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B879" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+    <row r="881" ht="24" customHeight="1">
+      <c r="A881" s="1" t="inlineStr">
+        <is>
+          <t>Sly Moore</t>
+        </is>
+      </c>
+    </row>
+    <row r="882" ht="24" customHeight="1">
+      <c r="A882" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B882" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="883" ht="24" customHeight="1">
+      <c r="A883" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B883" s="3" t="inlineStr">
+        <is>
+          <t>Sly Moore</t>
+        </is>
+      </c>
+    </row>
+    <row r="884" ht="24" customHeight="1">
+      <c r="A884" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B884" s="4" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+    </row>
+    <row r="885" ht="24" customHeight="1">
+      <c r="A885" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B885" s="3" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+    </row>
+    <row r="886" ht="24" customHeight="1">
+      <c r="A886" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B886" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="887" ht="24" customHeight="1">
+      <c r="A887" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B887" s="3" t="inlineStr">
+        <is>
+          <t>pale</t>
+        </is>
+      </c>
+    </row>
+    <row r="888" ht="24" customHeight="1">
+      <c r="A888" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B888" s="4" t="inlineStr">
+        <is>
+          <t>white</t>
+        </is>
+      </c>
+    </row>
+    <row r="889" ht="24" customHeight="1">
+      <c r="A889" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B889" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="890" ht="24" customHeight="1">
+      <c r="A890" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B890" s="4" t="inlineStr">
+        <is>
+          <t>female</t>
+        </is>
+      </c>
+    </row>
+    <row r="892" ht="24" customHeight="1">
+      <c r="A892" s="1" t="inlineStr">
+        <is>
+          <t>Tion Medon</t>
+        </is>
+      </c>
+    </row>
+    <row r="893" ht="24" customHeight="1">
+      <c r="A893" s="2" t="inlineStr">
+        <is>
+          <t>Field</t>
+        </is>
+      </c>
+      <c r="B893" s="2" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+    </row>
+    <row r="894" ht="24" customHeight="1">
+      <c r="A894" s="3" t="inlineStr">
+        <is>
+          <t>Name</t>
+        </is>
+      </c>
+      <c r="B894" s="3" t="inlineStr">
+        <is>
+          <t>Tion Medon</t>
+        </is>
+      </c>
+    </row>
+    <row r="895" ht="24" customHeight="1">
+      <c r="A895" s="4" t="inlineStr">
+        <is>
+          <t>Height</t>
+        </is>
+      </c>
+      <c r="B895" s="4" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+    </row>
+    <row r="896" ht="24" customHeight="1">
+      <c r="A896" s="3" t="inlineStr">
+        <is>
+          <t>Mass</t>
+        </is>
+      </c>
+      <c r="B896" s="3" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+    </row>
+    <row r="897" ht="24" customHeight="1">
+      <c r="A897" s="4" t="inlineStr">
+        <is>
+          <t>Hair Color</t>
+        </is>
+      </c>
+      <c r="B897" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+    </row>
+    <row r="898" ht="24" customHeight="1">
+      <c r="A898" s="3" t="inlineStr">
+        <is>
+          <t>Skin Color</t>
+        </is>
+      </c>
+      <c r="B898" s="3" t="inlineStr">
+        <is>
+          <t>grey</t>
+        </is>
+      </c>
+    </row>
+    <row r="899" ht="24" customHeight="1">
+      <c r="A899" s="4" t="inlineStr">
+        <is>
+          <t>Eye Color</t>
+        </is>
+      </c>
+      <c r="B899" s="4" t="inlineStr">
+        <is>
+          <t>black</t>
+        </is>
+      </c>
+    </row>
+    <row r="900" ht="24" customHeight="1">
+      <c r="A900" s="3" t="inlineStr">
+        <is>
+          <t>Birth Year</t>
+        </is>
+      </c>
+      <c r="B900" s="3" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+    </row>
+    <row r="901" ht="24" customHeight="1">
+      <c r="A901" s="4" t="inlineStr">
+        <is>
+          <t>Gender</t>
+        </is>
+      </c>
+      <c r="B901" s="4" t="inlineStr">
+        <is>
+          <t>male</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="82">
+    <mergeCell ref="A540:B540"/>
+    <mergeCell ref="A760:B760"/>
+    <mergeCell ref="A870:B870"/>
+    <mergeCell ref="A606:B606"/>
+    <mergeCell ref="A243:B243"/>
+    <mergeCell ref="A397:B397"/>
+    <mergeCell ref="A375:B375"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A826:B826"/>
+    <mergeCell ref="A804:B804"/>
+    <mergeCell ref="A309:B309"/>
+    <mergeCell ref="A738:B738"/>
+    <mergeCell ref="A716:B716"/>
+    <mergeCell ref="A188:B188"/>
+    <mergeCell ref="A771:B771"/>
+    <mergeCell ref="A661:B661"/>
+    <mergeCell ref="A111:B111"/>
+    <mergeCell ref="A353:B353"/>
+    <mergeCell ref="A782:B782"/>
+    <mergeCell ref="A232:B232"/>
+    <mergeCell ref="A595:B595"/>
+    <mergeCell ref="A45:B45"/>
+    <mergeCell ref="A287:B287"/>
+    <mergeCell ref="A452:B452"/>
+    <mergeCell ref="A694:B694"/>
+    <mergeCell ref="A727:B727"/>
+    <mergeCell ref="A364:B364"/>
+    <mergeCell ref="A177:B177"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A210:B210"/>
+    <mergeCell ref="A298:B298"/>
+    <mergeCell ref="A793:B793"/>
+    <mergeCell ref="A881:B881"/>
+    <mergeCell ref="A650:B650"/>
+    <mergeCell ref="A100:B100"/>
+    <mergeCell ref="A342:B342"/>
+    <mergeCell ref="A529:B529"/>
+    <mergeCell ref="A705:B705"/>
+    <mergeCell ref="A155:B155"/>
+    <mergeCell ref="A892:B892"/>
+    <mergeCell ref="A584:B584"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A276:B276"/>
+    <mergeCell ref="A441:B441"/>
+    <mergeCell ref="A166:B166"/>
+    <mergeCell ref="A639:B639"/>
+    <mergeCell ref="A496:B496"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="A859:B859"/>
+    <mergeCell ref="A628:B628"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A551:B551"/>
+    <mergeCell ref="A507:B507"/>
+    <mergeCell ref="A419:B419"/>
+    <mergeCell ref="A133:B133"/>
+    <mergeCell ref="A12:B12"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A617:B617"/>
+    <mergeCell ref="A67:B67"/>
+    <mergeCell ref="A518:B518"/>
+    <mergeCell ref="A672:B672"/>
+    <mergeCell ref="A430:B430"/>
+    <mergeCell ref="A408:B408"/>
+    <mergeCell ref="A837:B837"/>
+    <mergeCell ref="A221:B221"/>
+    <mergeCell ref="A485:B485"/>
+    <mergeCell ref="A463:B463"/>
+    <mergeCell ref="A683:B683"/>
+    <mergeCell ref="A749:B749"/>
+    <mergeCell ref="A474:B474"/>
+    <mergeCell ref="A562:B562"/>
+    <mergeCell ref="A331:B331"/>
+    <mergeCell ref="A254:B254"/>
+    <mergeCell ref="A144:B144"/>
+    <mergeCell ref="A122:B122"/>
+    <mergeCell ref="A386:B386"/>
+    <mergeCell ref="A573:B573"/>
+    <mergeCell ref="A815:B815"/>
+    <mergeCell ref="A199:B199"/>
+    <mergeCell ref="A265:B265"/>
+    <mergeCell ref="A848:B848"/>
+    <mergeCell ref="A320:B320"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/star_wars_order.xlsx
+++ b/star_wars_order.xlsx
@@ -14,6 +14,7 @@
     <sheet name="Planets" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Characters" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Vehicles" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Trivia" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,6 +47,12 @@
     <font>
       <name val="Arial"/>
       <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFD700"/>
       <sz val="11"/>
     </font>
   </fonts>
@@ -175,7 +182,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -202,6 +209,30 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10966,6 +10997,15 @@
           <t>Star Wars Vehicles</t>
         </is>
       </c>
+      <c r="B1" s="8" t="n"/>
+      <c r="C1" s="8" t="n"/>
+      <c r="D1" s="8" t="n"/>
+      <c r="E1" s="8" t="n"/>
+      <c r="F1" s="8" t="n"/>
+      <c r="G1" s="8" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="6" t="n"/>
     </row>
     <row r="2" ht="24" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
@@ -13053,4 +13093,480 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
+    <col width="10" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="11" t="inlineStr">
+        <is>
+          <t>Star Wars Trivia — 10 Questions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B2" s="12" t="inlineStr">
+        <is>
+          <t>Category</t>
+        </is>
+      </c>
+      <c r="C2" s="12" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="D2" s="12" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="E2" s="12" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="G2" s="12" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H2" s="12" t="inlineStr">
+        <is>
+          <t>Answer</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="52" customHeight="1">
+      <c r="A3" s="13" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>What language do Wookies speak?</t>
+        </is>
+      </c>
+      <c r="D3" s="14" t="inlineStr">
+        <is>
+          <t>Huttese</t>
+        </is>
+      </c>
+      <c r="E3" s="14" t="inlineStr">
+        <is>
+          <t>Shyriiwook</t>
+        </is>
+      </c>
+      <c r="F3" s="14" t="inlineStr">
+        <is>
+          <t>Galactic Basic</t>
+        </is>
+      </c>
+      <c r="G3" s="14" t="inlineStr">
+        <is>
+          <t>Ewokese</t>
+        </is>
+      </c>
+      <c r="H3" s="15" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="52" customHeight="1">
+      <c r="A4" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="16" t="inlineStr">
+        <is>
+          <t>Starships</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Who manufactures the Millennium Falcon?</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>Kuat Drive Yards</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>Sienar Fleet Systems</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>Incom Corporation</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Corellian Engineering Corporation</t>
+        </is>
+      </c>
+      <c r="H4" s="18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Starships</t>
+        </is>
+      </c>
+      <c r="C5" s="14" t="inlineStr">
+        <is>
+          <t>What is the length of the Death Star in meters?</t>
+        </is>
+      </c>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>1,600 m</t>
+        </is>
+      </c>
+      <c r="E5" s="14" t="inlineStr">
+        <is>
+          <t>19,000 m</t>
+        </is>
+      </c>
+      <c r="F5" s="14" t="inlineStr">
+        <is>
+          <t>120,000 m</t>
+        </is>
+      </c>
+      <c r="G5" s="14" t="inlineStr">
+        <is>
+          <t>3,170 m</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Which species is classified as a gastropod?</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>Rodian</t>
+        </is>
+      </c>
+      <c r="E6" s="17" t="inlineStr">
+        <is>
+          <t>Gungan</t>
+        </is>
+      </c>
+      <c r="F6" s="17" t="inlineStr">
+        <is>
+          <t>Hutt</t>
+        </is>
+      </c>
+      <c r="G6" s="17" t="inlineStr">
+        <is>
+          <t>Trandoshan</t>
+        </is>
+      </c>
+      <c r="H6" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Movie Order</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>In release order, which film was released 4th?</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>A New Hope</t>
+        </is>
+      </c>
+      <c r="E7" s="14" t="inlineStr">
+        <is>
+          <t>Return of the Jedi</t>
+        </is>
+      </c>
+      <c r="F7" s="14" t="inlineStr">
+        <is>
+          <t>The Phantom Menace</t>
+        </is>
+      </c>
+      <c r="G7" s="14" t="inlineStr">
+        <is>
+          <t>Attack of the Clones</t>
+        </is>
+      </c>
+      <c r="H7" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="16" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>Species</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>What is the average lifespan of a Wookie?</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>120 years</t>
+        </is>
+      </c>
+      <c r="E8" s="17" t="inlineStr">
+        <is>
+          <t>400 years</t>
+        </is>
+      </c>
+      <c r="F8" s="17" t="inlineStr">
+        <is>
+          <t>900 years</t>
+        </is>
+      </c>
+      <c r="G8" s="17" t="inlineStr">
+        <is>
+          <t>250 years</t>
+        </is>
+      </c>
+      <c r="H8" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="13" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>Movie Order</t>
+        </is>
+      </c>
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>How many Star Wars main saga films are listed in the spreadsheet?</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E9" s="14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="F9" s="14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="G9" s="14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H9" s="15" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>Movie Order</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>Which Star Wars film was released first in theaters?</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="inlineStr">
+        <is>
+          <t>The Phantom Menace</t>
+        </is>
+      </c>
+      <c r="E10" s="17" t="inlineStr">
+        <is>
+          <t>The Empire Strikes Back</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="inlineStr">
+        <is>
+          <t>A New Hope</t>
+        </is>
+      </c>
+      <c r="G10" s="17" t="inlineStr">
+        <is>
+          <t>Return of the Jedi</t>
+        </is>
+      </c>
+      <c r="H10" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="52" customHeight="1">
+      <c r="A11" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>Movie Order</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>What is the chronological position of 'Return of the Jedi'?</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>4th</t>
+        </is>
+      </c>
+      <c r="E11" s="14" t="inlineStr">
+        <is>
+          <t>5th</t>
+        </is>
+      </c>
+      <c r="F11" s="14" t="inlineStr">
+        <is>
+          <t>7th</t>
+        </is>
+      </c>
+      <c r="G11" s="14" t="inlineStr">
+        <is>
+          <t>6th</t>
+        </is>
+      </c>
+      <c r="H11" s="15" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Movie Order</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>Which film is #1 in chronological order?</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>The Phantom Menace</t>
+        </is>
+      </c>
+      <c r="E12" s="17" t="inlineStr">
+        <is>
+          <t>A New Hope</t>
+        </is>
+      </c>
+      <c r="F12" s="17" t="inlineStr">
+        <is>
+          <t>Attack of the Clones</t>
+        </is>
+      </c>
+      <c r="G12" s="17" t="inlineStr">
+        <is>
+          <t>Revenge of the Sith</t>
+        </is>
+      </c>
+      <c r="H12" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:H1"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>